--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484075_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484075_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.1716</v>
+        <v>12.6865</v>
       </c>
       <c r="E2" t="n">
-        <v>9.8934</v>
+        <v>10.3242</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2781</v>
+        <v>2.3623</v>
       </c>
       <c r="G2" t="n">
         <v>9.3843</v>
@@ -610,13 +610,13 @@
         <v>1.7855</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5617</v>
+        <v>-0.0468</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7368</v>
+        <v>-0.306</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1751</v>
+        <v>0.2592</v>
       </c>
       <c r="V2" t="n">
         <v>2.5555</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.0899</v>
+        <v>6.9391</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8211</v>
+        <v>4.3337</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2688</v>
+        <v>2.6054</v>
       </c>
       <c r="G3" t="n">
         <v>5.2391</v>
@@ -688,13 +688,13 @@
         <v>1.9838</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5929</v>
+        <v>0.4421</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5613</v>
+        <v>0.0738</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0317</v>
+        <v>0.3683</v>
       </c>
       <c r="V3" t="n">
         <v>0.266</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>M. ESTEBAN CALVO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6673</v>
+        <v>4.1308</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2339</v>
+        <v>2.4701</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4335</v>
+        <v>1.6607</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6769</v>
+        <v>3.7431</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0605</v>
+        <v>1.2246</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7374</v>
+        <v>2.5186</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2395</v>
+        <v>2.7648</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9985000000000001</v>
+        <v>1.4771</v>
       </c>
       <c r="L4" t="n">
-        <v>0.241</v>
+        <v>1.2877</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4374</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.059</v>
+        <v>-0.2525</v>
       </c>
       <c r="O4" t="n">
-        <v>1.4964</v>
+        <v>1.2309</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5871</v>
+        <v>1.7855</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5871</v>
+        <v>1.7855</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6693</v>
+        <v>-0.1913</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0056</v>
+        <v>-0.2947</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.1034</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.266</v>
+        <v>-1.2065</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.266</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. ESTEBAN CALVO</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4997</v>
+        <v>3.1212</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2037</v>
+        <v>1.0525</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2959</v>
+        <v>2.0687</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7431</v>
+        <v>1.6769</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2246</v>
+        <v>-0.0605</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5186</v>
+        <v>1.7374</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7648</v>
+        <v>1.2395</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4771</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2877</v>
+        <v>0.241</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.4374</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2525</v>
+        <v>-1.059</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2309</v>
+        <v>1.4964</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7855</v>
+        <v>1.5871</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7855</v>
+        <v>1.5871</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8225</v>
+        <v>0.1232</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5611</v>
+        <v>-0.187</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2614</v>
+        <v>0.3102</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2065</v>
+        <v>-0.266</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2065</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. SEVILLANO PUIG</t>
+          <t>N. BAQUES GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0158</v>
+        <v>2.8417</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3689</v>
+        <v>1.7041</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6469</v>
+        <v>1.1376</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1058</v>
+        <v>2.3695</v>
       </c>
       <c r="H6" t="n">
-        <v>2.913</v>
+        <v>0.0155</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.8073</v>
+        <v>2.354</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8619</v>
+        <v>2.1158</v>
       </c>
       <c r="K6" t="n">
-        <v>2.0215</v>
+        <v>-0.3417</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1596</v>
+        <v>2.4575</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2439</v>
+        <v>0.2537</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8915999999999999</v>
+        <v>0.3572</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.1035</v>
       </c>
       <c r="P6" t="n">
         <v>0.7935</v>
@@ -922,22 +922,22 @@
         <v>1.7855</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3825</v>
+        <v>0.282</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4989</v>
+        <v>-0.289</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8835</v>
+        <v>0.5709</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.266</v>
+        <v>-0.6032</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.8692</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.266</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2389</v>
+        <v>2.5739</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4705</v>
+        <v>0.8616</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7683</v>
+        <v>1.7122</v>
       </c>
       <c r="G7" t="n">
         <v>2.3727</v>
@@ -1000,13 +1000,13 @@
         <v>1.3887</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5306</v>
+        <v>-0.1956</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7481</v>
+        <v>-0.357</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2176</v>
+        <v>0.1615</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. BAQUES GARCIA</t>
+          <t>G. SEVILLANO PUIG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0604</v>
+        <v>2.3943</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0069</v>
+        <v>-0.0563</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0535</v>
+        <v>2.4505</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3695</v>
+        <v>1.1058</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0155</v>
+        <v>2.913</v>
       </c>
       <c r="I8" t="n">
-        <v>2.354</v>
+        <v>-1.8073</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1158</v>
+        <v>0.8619</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3417</v>
+        <v>2.0215</v>
       </c>
       <c r="L8" t="n">
-        <v>2.4575</v>
+        <v>-1.1596</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2537</v>
+        <v>0.2439</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3572</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1035</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="P8" t="n">
         <v>0.7935</v>
@@ -1078,22 +1078,22 @@
         <v>1.7855</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4994</v>
+        <v>0.7609</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9862</v>
+        <v>0.0738</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4868</v>
+        <v>0.6872</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6032</v>
+        <v>-0.266</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8692</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4724</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.0447</v>
+        <v>2.2627</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2401</v>
+        <v>0.7105</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8046</v>
+        <v>1.5521</v>
       </c>
       <c r="G9" t="n">
         <v>1.7487</v>
@@ -1156,13 +1156,13 @@
         <v>1.3887</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3077</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6744</v>
+        <v>-0.204</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9822</v>
+        <v>0.7297</v>
       </c>
       <c r="V9" t="n">
         <v>-0.4085</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3637</v>
+        <v>1.3912</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5864</v>
+        <v>-0.6431</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9501</v>
+        <v>2.0343</v>
       </c>
       <c r="G10" t="n">
         <v>0.9618</v>
@@ -1234,13 +1234,13 @@
         <v>1.5871</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1933</v>
+        <v>-0.1658</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1926</v>
+        <v>-0.2493</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0835</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3192</v>
+        <v>0.6323</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2453</v>
+        <v>-1.7919</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5645</v>
+        <v>2.4242</v>
       </c>
       <c r="G11" t="n">
         <v>2.1411</v>
@@ -1312,13 +1312,13 @@
         <v>1.5871</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4847</v>
+        <v>-0.1715</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6858</v>
+        <v>-0.2324</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2011</v>
+        <v>0.0608</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9405</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0124</v>
+        <v>0.0437</v>
       </c>
       <c r="E12" t="n">
         <v>0.2206</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.233</v>
+        <v>-0.1769</v>
       </c>
       <c r="G12" t="n">
         <v>-0.1235</v>
@@ -1390,13 +1390,13 @@
         <v>0.1984</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0873</v>
+        <v>-0.0312</v>
       </c>
       <c r="T12" t="n">
         <v>-0.1247</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0374</v>
+        <v>0.0935</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>37.4588</v>
+        <v>39.01739999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>17.6274</v>
+        <v>19.186</v>
       </c>
       <c r="F13" t="n">
-        <v>19.8312</v>
+        <v>19.8311</v>
       </c>
       <c r="G13" t="n">
         <v>30.6195</v>
@@ -1453,7 +1453,7 @@
         <v>3.4066</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8371999999999996</v>
+        <v>-0.8371999999999998</v>
       </c>
       <c r="O13" t="n">
         <v>4.243600000000001</v>
@@ -1468,13 +1468,13 @@
         <v>16.8629</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2270999999999999</v>
+        <v>1.3317</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.6551</v>
+        <v>-2.0965</v>
       </c>
       <c r="U13" t="n">
-        <v>3.4283</v>
+        <v>3.4282</v>
       </c>
       <c r="V13" t="n">
         <v>-0.8691999999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.2342</v>
+        <v>-0.3355</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5017</v>
+        <v>1.0119</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.736</v>
+        <v>-1.3474</v>
       </c>
       <c r="G14" t="n">
         <v>-1.3167</v>
@@ -1546,13 +1546,13 @@
         <v>0.9919</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.124</v>
+        <v>-0.2253</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1732</v>
+        <v>-0.6631</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0492</v>
+        <v>0.4378</v>
       </c>
       <c r="V14" t="n">
         <v>1.2065</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.864</v>
+        <v>-2.1318</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3549</v>
+        <v>0.9468</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.2189</v>
+        <v>-3.0786</v>
       </c>
       <c r="G15" t="n">
         <v>-0.7673</v>
@@ -1624,13 +1624,13 @@
         <v>0.7935</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7681</v>
+        <v>0.5003</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3742</v>
+        <v>-0.0339</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3939</v>
+        <v>0.5342</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6745</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. GARCIA MARTINEZ</t>
+          <t>A. ROSA BEJARANO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.1378</v>
+        <v>-2.3434</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0735</v>
+        <v>-1.4376</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2113</v>
+        <v>-0.9056999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.9713</v>
+        <v>-2.7218</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0862</v>
+        <v>-1.7333</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.8851</v>
+        <v>-0.9885</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4714</v>
+        <v>-0.3972</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4287</v>
+        <v>0.2027</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0427</v>
+        <v>-0.5999</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.4427</v>
+        <v>-2.3245</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5148</v>
+        <v>-1.9359</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.9278</v>
+        <v>-0.3886</v>
       </c>
       <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-0.9919</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-1.9838</v>
       </c>
       <c r="R16" t="n">
         <v>0.9919</v>
       </c>
       <c r="S16" t="n">
-        <v>0.619</v>
+        <v>0.3784</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1135</v>
+        <v>0.0228</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.3556</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4724</v>
+        <v>-0.0713</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.266</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. ROSA BEJARANO</t>
+          <t>R. HENRIQUE RIBEIRO FORMOSO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.5194</v>
+        <v>-2.559</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6417</v>
+        <v>-0.7648</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8777</v>
+        <v>-1.7942</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.7218</v>
+        <v>-2.4424</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.7333</v>
+        <v>-0.1662</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9885</v>
+        <v>-2.2762</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3972</v>
+        <v>0.338</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2027</v>
+        <v>0.2175</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5999</v>
+        <v>0.1205</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.3245</v>
+        <v>-2.7804</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.9359</v>
+        <v>-0.3837</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3886</v>
+        <v>-2.3967</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9919</v>
+        <v>0.7935</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2024</v>
+        <v>-0.5215</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1813</v>
+        <v>-0.7141</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3837</v>
+        <v>0.1926</v>
       </c>
       <c r="V17" t="n">
+        <v>0.6032</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.6032</v>
+      </c>
+      <c r="X17" t="n">
         <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>-0.0713</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.0713</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. HENRIQUE RIBEIRO FORMOSO</t>
+          <t>A. GARCIA MARTINEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.9909</v>
+        <v>-2.6802</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1729</v>
+        <v>-0.4367</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.818</v>
+        <v>-2.2436</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.4424</v>
+        <v>-2.9713</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1662</v>
+        <v>-0.0862</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.2762</v>
+        <v>-2.8851</v>
       </c>
       <c r="J18" t="n">
-        <v>0.338</v>
+        <v>0.4714</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2175</v>
+        <v>0.4287</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1205</v>
+        <v>0.0427</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.7804</v>
+        <v>-3.4427</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3837</v>
+        <v>-0.5148</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.3967</v>
+        <v>-2.9278</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1984</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9534</v>
+        <v>0.0765</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1222</v>
+        <v>-0.3967</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1688</v>
+        <v>0.4732</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6032</v>
+        <v>1.2065</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6032</v>
+        <v>1.4724</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.1795</v>
+        <v>-2.87</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.6985</v>
+        <v>-2.1884</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.481</v>
+        <v>-0.6816</v>
       </c>
       <c r="G19" t="n">
         <v>-3.4392</v>
@@ -1936,13 +1936,13 @@
         <v>1.1903</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5419</v>
+        <v>-0.2324</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3092</v>
+        <v>-0.7991</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7673</v>
+        <v>0.5667</v>
       </c>
       <c r="V19" t="n">
         <v>0.6032</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. NGOMO MIFUMU</t>
+          <t>A. FIGUERAS GÜELL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2563</v>
+        <v>-3.7604</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9445</v>
+        <v>-1.8286</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3117</v>
+        <v>-1.9317</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.332</v>
+        <v>-1.0788</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.8551</v>
+        <v>-0.01</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4768</v>
+        <v>-1.0688</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.4681</v>
+        <v>-0.0149</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.7127</v>
+        <v>-0.0149</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7554</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8638</v>
+        <v>-1.0639</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.1424</v>
+        <v>0.0049</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2786</v>
+        <v>-1.0688</v>
       </c>
       <c r="P20" t="n">
+        <v>-0.7935</v>
+      </c>
+      <c r="Q20" t="n">
         <v>-0.9919</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-1.9838</v>
-      </c>
       <c r="R20" t="n">
-        <v>0.9919</v>
+        <v>0.1984</v>
       </c>
       <c r="S20" t="n">
-        <v>2.3336</v>
+        <v>-0.0071</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2414</v>
+        <v>-0.1474</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0922</v>
+        <v>0.1403</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.266</v>
+        <v>-1.881</v>
       </c>
       <c r="W20" t="n">
-        <v>0.266</v>
+        <v>-0.6745</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.532</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. FIGUERAS GÜELL</t>
+          <t>O. NGOMO MIFUMU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9466</v>
+        <v>-4.4831</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9307</v>
+        <v>-3.8628</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0159</v>
+        <v>-0.6203</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0788</v>
+        <v>-4.332</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.01</v>
+        <v>-3.8551</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0688</v>
+        <v>-0.4768</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0149</v>
+        <v>-2.4681</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0149</v>
+        <v>-1.7127</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.7554</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0639</v>
+        <v>-1.8638</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0049</v>
+        <v>-2.1424</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0688</v>
+        <v>0.2786</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7935</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1984</v>
+        <v>0.9919</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1933</v>
+        <v>1.1067</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2494</v>
+        <v>0.3232</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0561</v>
+        <v>0.7836</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.881</v>
+        <v>-0.266</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6745</v>
+        <v>0.266</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2065</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.1963</v>
+        <v>-6.4021</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.3249</v>
+        <v>-4.8351</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8714</v>
+        <v>-1.567</v>
       </c>
       <c r="G22" t="n">
         <v>-6.0479</v>
@@ -2170,13 +2170,13 @@
         <v>0.9919</v>
       </c>
       <c r="S22" t="n">
-        <v>0.169</v>
+        <v>-0.0368</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0112</v>
+        <v>-0.5213</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1802</v>
+        <v>0.4845</v>
       </c>
       <c r="V22" t="n">
         <v>0.6745</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-10.1337</v>
+        <v>-9.212899999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.0481</v>
+        <v>-6.4359</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.0856</v>
+        <v>-2.777</v>
       </c>
       <c r="G23" t="n">
         <v>-5.5022</v>
@@ -2248,13 +2248,13 @@
         <v>0.9919</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0525</v>
+        <v>-0.1317</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1109</v>
+        <v>-0.4987</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0584</v>
+        <v>0.367</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6032</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-37.4587</v>
+        <v>-36.7784</v>
       </c>
       <c r="E24" t="n">
         <v>-19.8312</v>
       </c>
       <c r="F24" t="n">
-        <v>-17.6275</v>
+        <v>-16.9471</v>
       </c>
       <c r="G24" t="n">
-        <v>-30.6196</v>
+        <v>-30.61960000000001</v>
       </c>
       <c r="H24" t="n">
         <v>-12.4493</v>
@@ -2305,7 +2305,7 @@
         <v>0.8371000000000004</v>
       </c>
       <c r="L24" t="n">
-        <v>-4.2436</v>
+        <v>-4.243600000000001</v>
       </c>
       <c r="M24" t="n">
         <v>-27.2128</v>
@@ -2323,16 +2323,16 @@
         <v>-16.8624</v>
       </c>
       <c r="R24" t="n">
-        <v>8.927100000000001</v>
+        <v>8.927099999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2270000000000001</v>
+        <v>0.9071000000000001</v>
       </c>
       <c r="T24" t="n">
         <v>-3.4283</v>
       </c>
       <c r="U24" t="n">
-        <v>3.6553</v>
+        <v>4.3355</v>
       </c>
       <c r="V24" t="n">
         <v>0.8691999999999995</v>
